--- a/provider_specialty_cprd_V.0.1_summarised.xlsx
+++ b/provider_specialty_cprd_V.0.1_summarised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{43CD0B77-10A2-4547-A71B-81611BEB9C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB25439B-0B1C-4C6A-AF25-881738FC29CA}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{43CD0B77-10A2-4547-A71B-81611BEB9C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9975E06D-DA7E-4588-8EBE-93AE2C9D1FF9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3004D37C-F705-45AE-B4B1-1CCCB9000F2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="96">
   <si>
     <t>specialty_source_value</t>
   </si>
@@ -314,7 +314,16 @@
     <t>Medical Director</t>
   </si>
   <si>
-    <t>summarised</t>
+    <t>Nurse</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>General Practitioner</t>
+  </si>
+  <si>
+    <t>specialty_source_value_summarised</t>
   </si>
 </sst>
 </file>
@@ -405,6 +414,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -750,7 +763,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -764,7 +777,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -777,7 +790,9 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C4" s="3">
         <v>1</v>
       </c>
@@ -790,7 +805,7 @@
         <v>73</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -804,7 +819,7 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -818,7 +833,7 @@
         <v>75</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -831,7 +846,9 @@
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C8" s="3">
         <v>1</v>
       </c>
@@ -844,7 +861,7 @@
         <v>76</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -857,7 +874,9 @@
       <c r="A10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C10" s="3">
         <v>1</v>
       </c>
@@ -870,7 +889,7 @@
         <v>78</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -883,7 +902,9 @@
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C12" s="3">
         <v>1</v>
       </c>
@@ -895,7 +916,9 @@
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C13" s="3">
         <v>1</v>
       </c>
@@ -907,7 +930,9 @@
       <c r="A14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C14" s="3">
         <v>1</v>
       </c>
@@ -919,7 +944,9 @@
       <c r="A15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C15" s="3">
         <v>1</v>
       </c>
@@ -932,7 +959,7 @@
         <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -945,7 +972,9 @@
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C17" s="3">
         <v>1</v>
       </c>
@@ -957,7 +986,9 @@
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C18" s="3">
         <v>1</v>
       </c>
@@ -969,7 +1000,9 @@
       <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C19" s="3">
         <v>1</v>
       </c>
@@ -981,7 +1014,9 @@
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C20" s="3">
         <v>1</v>
       </c>
@@ -993,7 +1028,9 @@
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C21" s="3">
         <v>1</v>
       </c>
@@ -1005,6 +1042,9 @@
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C22" s="3">
         <v>1</v>
       </c>
@@ -1016,7 +1056,9 @@
       <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C23" s="3">
         <v>1</v>
       </c>
@@ -1028,7 +1070,9 @@
       <c r="A24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C24" s="3">
         <v>1</v>
       </c>
@@ -1040,7 +1084,9 @@
       <c r="A25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C25" s="3">
         <v>1</v>
       </c>
@@ -1052,7 +1098,9 @@
       <c r="A26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C26" s="3">
         <v>1</v>
       </c>
@@ -1064,7 +1112,9 @@
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C27" s="3">
         <v>1</v>
       </c>
@@ -1076,7 +1126,9 @@
       <c r="A28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C28" s="3">
         <v>1</v>
       </c>
@@ -1088,7 +1140,9 @@
       <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C29" s="3">
         <v>1</v>
       </c>
@@ -1100,7 +1154,9 @@
       <c r="A30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C30" s="3">
         <v>1</v>
       </c>
@@ -1112,7 +1168,9 @@
       <c r="A31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C31" s="3">
         <v>1</v>
       </c>
@@ -1124,7 +1182,9 @@
       <c r="A32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C32" s="3">
         <v>1</v>
       </c>
@@ -1136,7 +1196,9 @@
       <c r="A33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C33" s="3">
         <v>1</v>
       </c>
@@ -1148,7 +1210,9 @@
       <c r="A34" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C34" s="3">
         <v>1</v>
       </c>
@@ -1160,7 +1224,9 @@
       <c r="A35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C35" s="3">
         <v>1</v>
       </c>
@@ -1172,7 +1238,9 @@
       <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C36" s="3">
         <v>1</v>
       </c>
@@ -1184,7 +1252,9 @@
       <c r="A37" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C37" s="3">
         <v>1</v>
       </c>
@@ -1196,7 +1266,9 @@
       <c r="A38" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C38" s="3">
         <v>1</v>
       </c>
@@ -1208,6 +1280,9 @@
       <c r="A39" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="B39" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C39" s="3">
         <v>1</v>
       </c>
@@ -1219,7 +1294,9 @@
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C40" s="3">
         <v>1</v>
       </c>
@@ -1231,7 +1308,9 @@
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C41" s="3">
         <v>1</v>
       </c>
@@ -1243,7 +1322,9 @@
       <c r="A42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C42" s="3">
         <v>1</v>
       </c>
@@ -1255,7 +1336,9 @@
       <c r="A43" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C43" s="3">
         <v>1</v>
       </c>
@@ -1267,7 +1350,9 @@
       <c r="A44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C44" s="3">
         <v>1</v>
       </c>
@@ -1279,7 +1364,9 @@
       <c r="A45" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C45" s="3">
         <v>1</v>
       </c>
@@ -1292,7 +1379,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -1305,7 +1392,9 @@
       <c r="A47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C47" s="3">
         <v>1</v>
       </c>
@@ -1317,7 +1406,9 @@
       <c r="A48" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C48" s="3">
         <v>1</v>
       </c>
@@ -1329,7 +1420,9 @@
       <c r="A49" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C49" s="3">
         <v>1</v>
       </c>
@@ -1341,7 +1434,9 @@
       <c r="A50" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C50" s="3">
         <v>1</v>
       </c>
@@ -1353,7 +1448,9 @@
       <c r="A51" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C51" s="3">
         <v>1</v>
       </c>
@@ -1365,7 +1462,9 @@
       <c r="A52" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C52" s="3">
         <v>1</v>
       </c>
@@ -1377,7 +1476,9 @@
       <c r="A53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C53" s="3">
         <v>1</v>
       </c>
@@ -1389,7 +1490,9 @@
       <c r="A54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="3"/>
+      <c r="B54" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C54" s="3">
         <v>1</v>
       </c>
@@ -1401,7 +1504,9 @@
       <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C55" s="3">
         <v>1</v>
       </c>
@@ -1413,7 +1518,9 @@
       <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C56" s="3">
         <v>1</v>
       </c>
@@ -1425,7 +1532,9 @@
       <c r="A57" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C57" s="3">
         <v>1</v>
       </c>
@@ -1437,7 +1546,9 @@
       <c r="A58" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C58" s="3">
         <v>1</v>
       </c>
@@ -1449,7 +1560,9 @@
       <c r="A59" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C59" s="3">
         <v>1</v>
       </c>
@@ -1462,7 +1575,7 @@
         <v>87</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -1475,7 +1588,9 @@
       <c r="A61" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C61" s="3">
         <v>1</v>
       </c>
@@ -1487,7 +1602,9 @@
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B62" s="3"/>
+      <c r="B62" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C62" s="3">
         <v>1</v>
       </c>
@@ -1499,7 +1616,9 @@
       <c r="A63" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C63" s="3">
         <v>1</v>
       </c>
@@ -1511,7 +1630,9 @@
       <c r="A64" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B64" s="3"/>
+      <c r="B64" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C64" s="3">
         <v>1</v>
       </c>
@@ -1523,7 +1644,9 @@
       <c r="A65" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B65" s="3"/>
+      <c r="B65" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C65" s="3">
         <v>1</v>
       </c>
@@ -1535,7 +1658,9 @@
       <c r="A66" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B66" s="3"/>
+      <c r="B66" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C66" s="3">
         <v>1</v>
       </c>
@@ -1547,7 +1672,9 @@
       <c r="A67" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B67" s="3"/>
+      <c r="B67" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C67" s="3">
         <v>1</v>
       </c>
@@ -1559,7 +1686,9 @@
       <c r="A68" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C68" s="3">
         <v>1</v>
       </c>
@@ -1571,7 +1700,9 @@
       <c r="A69" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B69" s="3"/>
+      <c r="B69" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C69" s="3">
         <v>1</v>
       </c>
@@ -1583,7 +1714,9 @@
       <c r="A70" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B70" s="3"/>
+      <c r="B70" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C70" s="3">
         <v>1</v>
       </c>
@@ -1595,7 +1728,9 @@
       <c r="A71" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="3"/>
+      <c r="B71" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C71" s="3">
         <v>1</v>
       </c>
@@ -1608,7 +1743,7 @@
         <v>89</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -1621,7 +1756,9 @@
       <c r="A73" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B73" s="3"/>
+      <c r="B73" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C73" s="3">
         <v>1</v>
       </c>
@@ -1633,7 +1770,9 @@
       <c r="A74" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B74" s="3"/>
+      <c r="B74" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C74" s="3">
         <v>1</v>
       </c>
@@ -1645,7 +1784,9 @@
       <c r="A75" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="3"/>
+      <c r="B75" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C75" s="3">
         <v>1</v>
       </c>
@@ -1657,7 +1798,9 @@
       <c r="A76" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B76" s="3"/>
+      <c r="B76" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C76" s="3">
         <v>1</v>
       </c>
@@ -1669,7 +1812,9 @@
       <c r="A77" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B77" s="3"/>
+      <c r="B77" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C77" s="3">
         <v>1</v>
       </c>
@@ -1681,7 +1826,9 @@
       <c r="A78" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B78" s="3"/>
+      <c r="B78" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C78" s="3">
         <v>1</v>
       </c>
@@ -1693,7 +1840,9 @@
       <c r="A79" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B79" s="3"/>
+      <c r="B79" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C79" s="3">
         <v>1</v>
       </c>
@@ -1705,7 +1854,9 @@
       <c r="A80" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B80" s="3"/>
+      <c r="B80" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C80" s="3">
         <v>1</v>
       </c>
@@ -1717,7 +1868,9 @@
       <c r="A81" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B81" s="3"/>
+      <c r="B81" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C81" s="3">
         <v>1</v>
       </c>
@@ -1729,7 +1882,9 @@
       <c r="A82" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B82" s="3"/>
+      <c r="B82" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C82" s="3">
         <v>1</v>
       </c>
@@ -1741,7 +1896,9 @@
       <c r="A83" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B83" s="3"/>
+      <c r="B83" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C83" s="3">
         <v>1</v>
       </c>
@@ -1753,7 +1910,9 @@
       <c r="A84" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B84" s="3"/>
+      <c r="B84" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C84" s="3">
         <v>1</v>
       </c>
@@ -1765,7 +1924,9 @@
       <c r="A85" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B85" s="3"/>
+      <c r="B85" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C85" s="3">
         <v>1</v>
       </c>
@@ -1777,7 +1938,9 @@
       <c r="A86" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B86" s="3"/>
+      <c r="B86" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C86" s="3">
         <v>1</v>
       </c>
@@ -1789,7 +1952,9 @@
       <c r="A87" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B87" s="3"/>
+      <c r="B87" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C87" s="3">
         <v>1</v>
       </c>
@@ -1801,7 +1966,9 @@
       <c r="A88" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B88" s="3"/>
+      <c r="B88" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C88" s="3">
         <v>1</v>
       </c>
@@ -1813,6 +1980,9 @@
       <c r="A89" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="B89" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C89" s="3">
         <v>1</v>
       </c>
@@ -1824,7 +1994,9 @@
       <c r="A90" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B90" s="3"/>
+      <c r="B90" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C90" s="3">
         <v>1</v>
       </c>

--- a/provider_specialty_cprd_V.0.1_summarised.xlsx
+++ b/provider_specialty_cprd_V.0.1_summarised.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,6 +41,9 @@
     <t>specialty_source_value</t>
   </si>
   <si>
+    <t>specialty_source_value_summarised</t>
+  </si>
+  <si>
     <t>Include</t>
   </si>
   <si>
@@ -50,18 +53,57 @@
     <t>General Medical Practitioner</t>
   </si>
   <si>
+    <t>General Practitioner</t>
+  </si>
+  <si>
+    <t>Community Practitioner</t>
+  </si>
+  <si>
     <t>Health Care Support Worker</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Salaried General Practitioner</t>
+  </si>
+  <si>
+    <t>Sessional GP</t>
+  </si>
+  <si>
+    <t>GP Registrar</t>
+  </si>
+  <si>
     <t>Consultant</t>
   </si>
   <si>
+    <t>Locum GP</t>
+  </si>
+  <si>
+    <t>Community Nurse</t>
+  </si>
+  <si>
+    <t>Nurse</t>
+  </si>
+  <si>
+    <t>Associate Practitioner - General Practitioner</t>
+  </si>
+  <si>
     <t>Physiotherapist</t>
   </si>
   <si>
     <t>Practitioner</t>
   </si>
   <si>
+    <t>Paramedic Specialist Practitioner</t>
+  </si>
+  <si>
+    <t>Medical Technical Officer - Pharmacy</t>
+  </si>
+  <si>
+    <t>Advanced Practitioner</t>
+  </si>
+  <si>
     <t>Paramedic</t>
   </si>
   <si>
@@ -137,6 +179,21 @@
     <t>Therapist</t>
   </si>
   <si>
+    <t>Medical Technical Officer</t>
+  </si>
+  <si>
+    <t>Sister/Charge Nurse</t>
+  </si>
+  <si>
+    <t>Paramedic Consultant</t>
+  </si>
+  <si>
+    <t>Senior House Officer</t>
+  </si>
+  <si>
+    <t>Art Therapist Specialist Practitioner</t>
+  </si>
+  <si>
     <t>Other Community Health Service - Social Care Worker</t>
   </si>
   <si>
@@ -176,6 +233,9 @@
     <t>Associate Practitioner - Nurse</t>
   </si>
   <si>
+    <t>Art Therapist Consultant</t>
+  </si>
+  <si>
     <t>Specialist Registrar</t>
   </si>
   <si>
@@ -206,12 +266,24 @@
     <t>Trust Grade Doctor - Career Grade level</t>
   </si>
   <si>
+    <t>Trust Grade Doctor - Specialist Registrar level</t>
+  </si>
+  <si>
+    <t>Multi Therapist Specialist Practitioner</t>
+  </si>
+  <si>
     <t>Approved Social Worker</t>
   </si>
   <si>
     <t>Clinical Medical Officer</t>
   </si>
   <si>
+    <t>Asst. Clinical Medical Officer</t>
+  </si>
+  <si>
+    <t>Medical Director</t>
+  </si>
+  <si>
     <t>Psychiatrist</t>
   </si>
   <si>
@@ -252,78 +324,6 @@
   </si>
   <si>
     <t>Community Learning Disabilities Nurse</t>
-  </si>
-  <si>
-    <t>Community Practitioner</t>
-  </si>
-  <si>
-    <t>Salaried General Practitioner</t>
-  </si>
-  <si>
-    <t>Sessional GP</t>
-  </si>
-  <si>
-    <t>GP Registrar</t>
-  </si>
-  <si>
-    <t>Locum GP</t>
-  </si>
-  <si>
-    <t>Community Nurse</t>
-  </si>
-  <si>
-    <t>Associate Practitioner - General Practitioner</t>
-  </si>
-  <si>
-    <t>Paramedic Specialist Practitioner</t>
-  </si>
-  <si>
-    <t>Medical Technical Officer - Pharmacy</t>
-  </si>
-  <si>
-    <t>Advanced Practitioner</t>
-  </si>
-  <si>
-    <t>Medical Technical Officer</t>
-  </si>
-  <si>
-    <t>Sister/Charge Nurse</t>
-  </si>
-  <si>
-    <t>Paramedic Consultant</t>
-  </si>
-  <si>
-    <t>Senior House Officer</t>
-  </si>
-  <si>
-    <t>Art Therapist Specialist Practitioner</t>
-  </si>
-  <si>
-    <t>Art Therapist Consultant</t>
-  </si>
-  <si>
-    <t>Trust Grade Doctor - Specialist Registrar level</t>
-  </si>
-  <si>
-    <t>Multi Therapist Specialist Practitioner</t>
-  </si>
-  <si>
-    <t>Asst. Clinical Medical Officer</t>
-  </si>
-  <si>
-    <t>Medical Director</t>
-  </si>
-  <si>
-    <t>Nurse</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>General Practitioner</t>
-  </si>
-  <si>
-    <t>specialty_source_value_summarised</t>
   </si>
 </sst>
 </file>
@@ -333,7 +333,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,10 +414,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -738,32 +734,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850DA912-8928-4DCB-8A8A-6E43E93CB520}">
   <dimension ref="A1:D90"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.44140625" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -772,12 +768,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -786,12 +782,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -800,12 +796,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -814,12 +810,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -828,12 +824,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -842,12 +838,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -856,12 +852,12 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -870,12 +866,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -884,12 +880,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -898,12 +894,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -912,12 +908,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -926,12 +922,12 @@
         <v>26.74540816326531</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -940,12 +936,12 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -954,12 +950,12 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -968,12 +964,12 @@
         <v>26.74540816326531</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -982,12 +978,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -996,12 +992,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
@@ -1010,12 +1006,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -1024,12 +1020,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C21" s="3">
         <v>1</v>
@@ -1038,12 +1034,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -1052,12 +1048,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1066,12 +1062,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1080,12 +1076,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -1094,12 +1090,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -1108,12 +1104,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -1122,12 +1118,12 @@
         <v>26.74540816326531</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -1136,12 +1132,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C29" s="3">
         <v>1</v>
@@ -1150,12 +1146,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -1164,12 +1160,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
@@ -1178,12 +1174,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -1192,12 +1188,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C33" s="3">
         <v>1</v>
@@ -1206,12 +1202,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -1220,12 +1216,12 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C35" s="3">
         <v>1</v>
@@ -1234,12 +1230,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -1248,12 +1244,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C37" s="3">
         <v>1</v>
@@ -1262,12 +1258,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -1276,12 +1272,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C39" s="3">
         <v>1</v>
@@ -1290,12 +1286,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -1304,12 +1300,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C41" s="3">
         <v>1</v>
@@ -1318,12 +1314,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" s="3" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -1332,12 +1328,12 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C43" s="3">
         <v>1</v>
@@ -1346,12 +1342,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -1360,12 +1356,12 @@
         <v>26.75</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45" s="3" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C45" s="3">
         <v>1</v>
@@ -1374,12 +1370,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46" s="3" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -1388,12 +1384,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -1402,12 +1398,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48" s="3" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -1416,12 +1412,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C49" s="3">
         <v>1</v>
@@ -1430,12 +1426,12 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -1444,12 +1440,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C51" s="3">
         <v>1</v>
@@ -1458,12 +1454,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -1472,12 +1468,12 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="A53" s="3" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C53" s="3">
         <v>1</v>
@@ -1486,12 +1482,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="A54" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -1500,12 +1496,12 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" s="3" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C55" s="3">
         <v>1</v>
@@ -1514,12 +1510,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -1528,12 +1524,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C57" s="3">
         <v>1</v>
@@ -1542,12 +1538,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -1556,12 +1552,12 @@
         <v>107.26</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="A59" s="3" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C59" s="3">
         <v>1</v>
@@ -1570,12 +1566,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60" s="3" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -1584,12 +1580,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="A61" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C61" s="3">
         <v>1</v>
@@ -1598,12 +1594,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="A62" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -1612,12 +1608,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4">
       <c r="A63" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C63" s="3">
         <v>1</v>
@@ -1626,12 +1622,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="A64" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -1640,12 +1636,12 @@
         <v>30.741666666666667</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4">
       <c r="A65" s="3" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C65" s="3">
         <v>1</v>
@@ -1654,12 +1650,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4">
       <c r="A66" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -1668,12 +1664,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C67" s="3">
         <v>1</v>
@@ -1682,12 +1678,12 @@
         <v>156.82</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -1696,12 +1692,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C69" s="3">
         <v>1</v>
@@ -1710,12 +1706,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4">
       <c r="A70" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -1724,12 +1720,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4">
       <c r="A71" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C71" s="3">
         <v>1</v>
@@ -1738,12 +1734,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4">
       <c r="A72" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -1752,12 +1748,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73" s="3" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C73" s="3">
         <v>1</v>
@@ -1766,12 +1762,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -1780,12 +1776,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C75" s="3">
         <v>1</v>
@@ -1794,12 +1790,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -1808,12 +1804,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C77" s="3">
         <v>1</v>
@@ -1822,12 +1818,12 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78" s="3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -1836,12 +1832,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4">
       <c r="A79" s="3" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C79" s="3">
         <v>1</v>
@@ -1850,12 +1846,12 @@
         <v>26.74540816326531</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4">
       <c r="A80" s="3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -1864,12 +1860,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4">
       <c r="A81" s="3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C81" s="3">
         <v>1</v>
@@ -1878,12 +1874,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4">
       <c r="A82" s="3" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
@@ -1892,12 +1888,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4">
       <c r="A83" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C83" s="3">
         <v>1</v>
@@ -1906,12 +1902,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4">
       <c r="A84" s="3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -1920,12 +1916,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4">
       <c r="A85" s="3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C85" s="3">
         <v>1</v>
@@ -1934,12 +1930,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4">
       <c r="A86" s="3" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -1948,12 +1944,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4">
       <c r="A87" s="3" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C87" s="3">
         <v>1</v>
@@ -1962,12 +1958,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4">
       <c r="A88" s="3" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -1976,12 +1972,12 @@
         <v>19.196153846153848</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4">
       <c r="A89" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C89" s="3">
         <v>1</v>
@@ -1990,12 +1986,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4">
       <c r="A90" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
